--- a/output/pdf_financials_xlsx/BLGV.xlsx
+++ b/output/pdf_financials_xlsx/BLGV.xlsx
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>14.292602</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>14.478427</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>15.979628</v>
       </c>
     </row>
     <row r="93">
@@ -3083,7 +3083,11 @@
           <t>Reserves (notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3428,7 +3432,11 @@
           <t>Reserves (notes 6 and 7)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>14.292602</v>
       </c>

--- a/output/pdf_financials_xlsx/BLGV.xlsx
+++ b/output/pdf_financials_xlsx/BLGV.xlsx
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.21933</v>
+        <v>1.580205</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.042771</v>
+        <v>1.208028</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.7337050000000001</v>
+        <v>5.803547</v>
       </c>
     </row>
     <row r="11">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.07457900000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.356641</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.022604</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.07457900000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.356641</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.022604</v>
       </c>
     </row>
     <row r="37">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5700,17 +5700,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>-1.580205</v>
+        <v>1.580205</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>-1.208028</v>
+        <v>1.208028</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-5.803547</v>
+        <v>5.803547</v>
       </c>
     </row>
     <row r="100">

--- a/output/pdf_financials_xlsx/BLGV.xlsx
+++ b/output/pdf_financials_xlsx/BLGV.xlsx
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.146794</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.092292</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.556686</v>
       </c>
     </row>
     <row r="68">
@@ -2320,10 +2320,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.326687</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.070392</v>
       </c>
     </row>
     <row r="116">
@@ -3808,7 +3808,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
